--- a/BC Network 2026 v8.xlsx
+++ b/BC Network 2026 v8.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -57,8 +57,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E40AF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00C25A00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +91,12 @@
         <bgColor rgb="00FFF7ED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8F0"/>
+        <bgColor rgb="00D5E8F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -90,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,6 +141,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -639,16 +662,16 @@
           <t>Appendix B (vision, page 123)</t>
         </is>
       </c>
-      <c r="W2" s="12" t="n">
+      <c r="W2" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="X2" s="12" t="n">
+      <c r="X2" s="14" t="n">
         <v>115</v>
       </c>
-      <c r="Y2" s="12" t="n">
+      <c r="Y2" s="14" t="n">
         <v>116</v>
       </c>
-      <c r="Z2" s="12" t="inlineStr">
+      <c r="Z2" s="14" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -738,16 +761,16 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W3" s="12" t="n">
+      <c r="W3" s="14" t="n">
         <v>72</v>
       </c>
-      <c r="X3" s="12" t="n">
+      <c r="X3" s="14" t="n">
         <v>136</v>
       </c>
-      <c r="Y3" s="12" t="n">
+      <c r="Y3" s="14" t="n">
         <v>140</v>
       </c>
-      <c r="Z3" s="12" t="inlineStr">
+      <c r="Z3" s="14" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -846,16 +869,16 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W4" s="12" t="n">
+      <c r="W4" s="14" t="n">
         <v>72</v>
       </c>
-      <c r="X4" s="12" t="n">
+      <c r="X4" s="14" t="n">
         <v>125</v>
       </c>
-      <c r="Y4" s="12" t="n">
+      <c r="Y4" s="14" t="n">
         <v>128</v>
       </c>
-      <c r="Z4" s="12" t="inlineStr">
+      <c r="Z4" s="14" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -946,16 +969,16 @@
           <t>Appendix B (vision, page 124)</t>
         </is>
       </c>
-      <c r="W5" s="12" t="n">
+      <c r="W5" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="X5" s="12" t="n">
+      <c r="X5" s="14" t="n">
         <v>108</v>
       </c>
-      <c r="Y5" s="12" t="n">
+      <c r="Y5" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="Z5" s="12" t="inlineStr">
+      <c r="Z5" s="14" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -1046,16 +1069,16 @@
           <t>Appendix B (vision, page 130)</t>
         </is>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="X6" s="12" t="n">
+      <c r="X6" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="Y6" s="12" t="n">
+      <c r="Y6" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="Z6" s="12" t="inlineStr">
+      <c r="Z6" s="14" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -1149,16 +1172,16 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W7" s="13" t="n">
+      <c r="W7" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="X7" s="13" t="n">
+      <c r="X7" s="15" t="n">
         <v>115</v>
       </c>
-      <c r="Y7" s="13" t="n">
+      <c r="Y7" s="15" t="n">
         <v>117</v>
       </c>
-      <c r="Z7" s="13" t="inlineStr">
+      <c r="Z7" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -1183,10 +1206,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="E8" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -1259,20 +1280,10 @@
           <t>Appendix B (vision, page 136)</t>
         </is>
       </c>
-      <c r="W8" s="13" t="n">
-        <v>96</v>
-      </c>
-      <c r="X8" s="13" t="n">
-        <v>166</v>
-      </c>
-      <c r="Y8" s="13" t="n">
-        <v>168</v>
-      </c>
-      <c r="Z8" s="13" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
-        </is>
-      </c>
+      <c r="W8" s="16" t="n"/>
+      <c r="X8" s="16" t="n"/>
+      <c r="Y8" s="16" t="n"/>
+      <c r="Z8" s="16" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1353,16 +1364,16 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W9" s="13" t="n">
+      <c r="W9" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="X9" s="13" t="n">
+      <c r="X9" s="15" t="n">
         <v>123</v>
       </c>
-      <c r="Y9" s="13" t="n">
+      <c r="Y9" s="15" t="n">
         <v>125</v>
       </c>
-      <c r="Z9" s="13" t="inlineStr">
+      <c r="Z9" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -1461,16 +1472,16 @@
           <t>Appendix B (vision, page 133)</t>
         </is>
       </c>
-      <c r="W10" s="13" t="n">
+      <c r="W10" s="15" t="n">
         <v>69</v>
       </c>
-      <c r="X10" s="13" t="n">
+      <c r="X10" s="15" t="n">
         <v>139</v>
       </c>
-      <c r="Y10" s="13" t="n">
+      <c r="Y10" s="15" t="n">
         <v>141</v>
       </c>
-      <c r="Z10" s="13" t="inlineStr">
+      <c r="Z10" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -1564,16 +1575,16 @@
           <t>Appendix B (vision, page 132)</t>
         </is>
       </c>
-      <c r="W11" s="13" t="n">
+      <c r="W11" s="15" t="n">
         <v>66</v>
       </c>
-      <c r="X11" s="13" t="n">
+      <c r="X11" s="15" t="n">
         <v>136</v>
       </c>
-      <c r="Y11" s="13" t="n">
+      <c r="Y11" s="15" t="n">
         <v>138</v>
       </c>
-      <c r="Z11" s="13" t="inlineStr">
+      <c r="Z11" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -1672,16 +1683,16 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W12" s="13" t="n">
+      <c r="W12" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="X12" s="13" t="n">
+      <c r="X12" s="15" t="n">
         <v>115</v>
       </c>
-      <c r="Y12" s="13" t="n">
+      <c r="Y12" s="15" t="n">
         <v>117</v>
       </c>
-      <c r="Z12" s="13" t="inlineStr">
+      <c r="Z12" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -1782,16 +1793,16 @@
           <t>Appendix B (vision, page 129)</t>
         </is>
       </c>
-      <c r="W13" s="13" t="n">
+      <c r="W13" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="X13" s="13" t="n">
+      <c r="X13" s="15" t="n">
         <v>114</v>
       </c>
-      <c r="Y13" s="13" t="n">
+      <c r="Y13" s="15" t="n">
         <v>116</v>
       </c>
-      <c r="Z13" s="13" t="inlineStr">
+      <c r="Z13" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -1816,10 +1827,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="E14" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1892,20 +1901,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W14" s="13" t="n">
-        <v>59</v>
-      </c>
-      <c r="X14" s="13" t="n">
-        <v>129</v>
-      </c>
-      <c r="Y14" s="13" t="n">
-        <v>131</v>
-      </c>
-      <c r="Z14" s="13" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
-        </is>
-      </c>
+      <c r="W14" s="16" t="n"/>
+      <c r="X14" s="16" t="n"/>
+      <c r="Y14" s="16" t="n"/>
+      <c r="Z14" s="16" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1992,16 +1991,16 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W15" s="13" t="n">
+      <c r="W15" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="X15" s="13" t="n">
+      <c r="X15" s="15" t="n">
         <v>103</v>
       </c>
-      <c r="Y15" s="13" t="n">
+      <c r="Y15" s="15" t="n">
         <v>105</v>
       </c>
-      <c r="Z15" s="13" t="inlineStr">
+      <c r="Z15" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -2100,16 +2099,16 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W16" s="13" t="n">
+      <c r="W16" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="X16" s="13" t="n">
+      <c r="X16" s="15" t="n">
         <v>118</v>
       </c>
-      <c r="Y16" s="13" t="n">
+      <c r="Y16" s="15" t="n">
         <v>120</v>
       </c>
-      <c r="Z16" s="13" t="inlineStr">
+      <c r="Z16" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -2210,16 +2209,16 @@
           <t>Appendix B (vision, page 163)</t>
         </is>
       </c>
-      <c r="W17" s="12" t="n">
+      <c r="W17" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="X17" s="12" t="n">
+      <c r="X17" s="14" t="n">
         <v>77</v>
       </c>
-      <c r="Y17" s="12" t="n">
+      <c r="Y17" s="14" t="n">
         <v>81</v>
       </c>
-      <c r="Z17" s="12" t="inlineStr">
+      <c r="Z17" s="14" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -2320,16 +2319,16 @@
           <t>Appendix B (vision, page 151)</t>
         </is>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="X18" s="12" t="n">
+      <c r="X18" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="Y18" s="12" t="n">
+      <c r="Y18" s="14" t="n">
         <v>132</v>
       </c>
-      <c r="Z18" s="12" t="inlineStr">
+      <c r="Z18" s="14" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -2428,16 +2427,16 @@
           <t>Appendix B (vision, page 144)</t>
         </is>
       </c>
-      <c r="W19" s="13" t="n">
+      <c r="W19" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="X19" s="13" t="n">
+      <c r="X19" s="15" t="n">
         <v>74</v>
       </c>
-      <c r="Y19" s="13" t="n">
+      <c r="Y19" s="15" t="n">
         <v>76</v>
       </c>
-      <c r="Z19" s="13" t="inlineStr">
+      <c r="Z19" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -2462,10 +2461,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="E20" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -2531,20 +2528,10 @@
           <t>Appendix B (vision, page 157)</t>
         </is>
       </c>
-      <c r="W20" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="X20" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y20" s="13" t="n">
-        <v>102</v>
-      </c>
-      <c r="Z20" s="13" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
-        </is>
-      </c>
+      <c r="W20" s="16" t="n"/>
+      <c r="X20" s="16" t="n"/>
+      <c r="Y20" s="16" t="n"/>
+      <c r="Z20" s="16" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -2639,16 +2626,16 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W21" s="13" t="n">
+      <c r="W21" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="X21" s="13" t="n">
+      <c r="X21" s="15" t="n">
         <v>87</v>
       </c>
-      <c r="Y21" s="13" t="n">
+      <c r="Y21" s="15" t="n">
         <v>89</v>
       </c>
-      <c r="Z21" s="13" t="inlineStr">
+      <c r="Z21" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -2744,16 +2731,16 @@
           <t>Appendix B (vision, page 162)</t>
         </is>
       </c>
-      <c r="W22" s="13" t="n">
+      <c r="W22" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="X22" s="13" t="n">
+      <c r="X22" s="15" t="n">
         <v>83</v>
       </c>
-      <c r="Y22" s="13" t="n">
+      <c r="Y22" s="15" t="n">
         <v>85</v>
       </c>
-      <c r="Z22" s="13" t="inlineStr">
+      <c r="Z22" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -2852,16 +2839,16 @@
           <t>Appendix B (vision, page 153)</t>
         </is>
       </c>
-      <c r="W23" s="13" t="n">
+      <c r="W23" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="X23" s="13" t="n">
+      <c r="X23" s="15" t="n">
         <v>89</v>
       </c>
-      <c r="Y23" s="13" t="n">
+      <c r="Y23" s="15" t="n">
         <v>91</v>
       </c>
-      <c r="Z23" s="13" t="inlineStr">
+      <c r="Z23" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -2962,16 +2949,16 @@
           <t>Appendix B (vision, page 149)</t>
         </is>
       </c>
-      <c r="W24" s="13" t="n">
+      <c r="W24" s="15" t="n">
         <v>-11</v>
       </c>
-      <c r="X24" s="13" t="n">
+      <c r="X24" s="15" t="n">
         <v>59</v>
       </c>
-      <c r="Y24" s="13" t="n">
+      <c r="Y24" s="15" t="n">
         <v>61</v>
       </c>
-      <c r="Z24" s="13" t="inlineStr">
+      <c r="Z24" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -3065,16 +3052,16 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W25" s="13" t="n">
+      <c r="W25" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="X25" s="13" t="n">
+      <c r="X25" s="15" t="n">
         <v>77</v>
       </c>
-      <c r="Y25" s="13" t="n">
+      <c r="Y25" s="15" t="n">
         <v>79</v>
       </c>
-      <c r="Z25" s="13" t="inlineStr">
+      <c r="Z25" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -3156,16 +3143,16 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W26" s="13" t="n">
+      <c r="W26" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="X26" s="13" t="n">
+      <c r="X26" s="15" t="n">
         <v>72</v>
       </c>
-      <c r="Y26" s="13" t="n">
+      <c r="Y26" s="15" t="n">
         <v>74</v>
       </c>
-      <c r="Z26" s="13" t="inlineStr">
+      <c r="Z26" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -3266,16 +3253,16 @@
           <t>Appendix B (vision, page 161)</t>
         </is>
       </c>
-      <c r="W27" s="13" t="n">
+      <c r="W27" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="X27" s="13" t="n">
+      <c r="X27" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="Y27" s="13" t="n">
+      <c r="Y27" s="15" t="n">
         <v>102</v>
       </c>
-      <c r="Z27" s="13" t="inlineStr">
+      <c r="Z27" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -3365,16 +3352,16 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W28" s="13" t="n">
+      <c r="W28" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="X28" s="13" t="n">
+      <c r="X28" s="15" t="n">
         <v>94</v>
       </c>
-      <c r="Y28" s="13" t="n">
+      <c r="Y28" s="15" t="n">
         <v>96</v>
       </c>
-      <c r="Z28" s="13" t="inlineStr">
+      <c r="Z28" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -3470,16 +3457,16 @@
           <t>Appendix B (vision, page 162)</t>
         </is>
       </c>
-      <c r="W29" s="13" t="n">
+      <c r="W29" s="15" t="n">
         <v>145</v>
       </c>
-      <c r="X29" s="13" t="n">
+      <c r="X29" s="15" t="n">
         <v>215</v>
       </c>
-      <c r="Y29" s="13" t="n">
+      <c r="Y29" s="15" t="n">
         <v>217</v>
       </c>
-      <c r="Z29" s="13" t="inlineStr">
+      <c r="Z29" s="15" t="inlineStr">
         <is>
           <t>2022 Mirror</t>
         </is>
@@ -3578,6 +3565,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W30" s="16" t="n"/>
+      <c r="X30" s="16" t="n"/>
+      <c r="Y30" s="16" t="n"/>
+      <c r="Z30" s="16" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -3674,6 +3665,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W31" s="16" t="n"/>
+      <c r="X31" s="16" t="n"/>
+      <c r="Y31" s="16" t="n"/>
+      <c r="Z31" s="16" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -3770,6 +3765,10 @@
           <t>Appendix B (vision, page 135)</t>
         </is>
       </c>
+      <c r="W32" s="16" t="n"/>
+      <c r="X32" s="16" t="n"/>
+      <c r="Y32" s="16" t="n"/>
+      <c r="Z32" s="16" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -3864,6 +3863,10 @@
           <t>Appendix B (vision, page 132)</t>
         </is>
       </c>
+      <c r="W33" s="16" t="n"/>
+      <c r="X33" s="16" t="n"/>
+      <c r="Y33" s="16" t="n"/>
+      <c r="Z33" s="16" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -3958,6 +3961,10 @@
           <t>Appendix B (vision, page 131)</t>
         </is>
       </c>
+      <c r="W34" s="16" t="n"/>
+      <c r="X34" s="16" t="n"/>
+      <c r="Y34" s="16" t="n"/>
+      <c r="Z34" s="16" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -4054,6 +4061,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W35" s="16" t="n"/>
+      <c r="X35" s="16" t="n"/>
+      <c r="Y35" s="16" t="n"/>
+      <c r="Z35" s="16" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -4150,6 +4161,10 @@
           <t>Appendix B (vision, page 129)</t>
         </is>
       </c>
+      <c r="W36" s="16" t="n"/>
+      <c r="X36" s="16" t="n"/>
+      <c r="Y36" s="16" t="n"/>
+      <c r="Z36" s="16" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -4246,6 +4261,10 @@
           <t>Appendix B (vision, page 130)</t>
         </is>
       </c>
+      <c r="W37" s="16" t="n"/>
+      <c r="X37" s="16" t="n"/>
+      <c r="Y37" s="16" t="n"/>
+      <c r="Z37" s="16" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -4342,6 +4361,10 @@
           <t>Appendix B (vision, page 124)</t>
         </is>
       </c>
+      <c r="W38" s="16" t="n"/>
+      <c r="X38" s="16" t="n"/>
+      <c r="Y38" s="16" t="n"/>
+      <c r="Z38" s="16" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -4438,6 +4461,10 @@
           <t>Appendix B (vision, page 125)</t>
         </is>
       </c>
+      <c r="W39" s="16" t="n"/>
+      <c r="X39" s="16" t="n"/>
+      <c r="Y39" s="16" t="n"/>
+      <c r="Z39" s="16" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -4534,6 +4561,10 @@
           <t>Appendix B (vision, page 125)</t>
         </is>
       </c>
+      <c r="W40" s="16" t="n"/>
+      <c r="X40" s="16" t="n"/>
+      <c r="Y40" s="16" t="n"/>
+      <c r="Z40" s="16" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -4595,6 +4626,10 @@
           <t>Not in BBGM. From 2025-12 Tables</t>
         </is>
       </c>
+      <c r="W41" s="16" t="n"/>
+      <c r="X41" s="16" t="n"/>
+      <c r="Y41" s="16" t="n"/>
+      <c r="Z41" s="16" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -4656,6 +4691,10 @@
           <t>Not in BBGM. From 2025-12 Tables</t>
         </is>
       </c>
+      <c r="W42" s="16" t="n"/>
+      <c r="X42" s="16" t="n"/>
+      <c r="Y42" s="16" t="n"/>
+      <c r="Z42" s="16" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -4676,10 +4715,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E43" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4752,6 +4789,20 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W43" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="X43" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y43" s="14" t="n">
+        <v>113</v>
+      </c>
+      <c r="Z43" s="14" t="inlineStr">
+        <is>
+          <t>2022 GSP</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -4770,10 +4821,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E44" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -4831,6 +4880,20 @@
           <t>Appendix B (vision, page 157)</t>
         </is>
       </c>
+      <c r="W44" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="X44" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="Y44" s="14" t="n">
+        <v>107</v>
+      </c>
+      <c r="Z44" s="14" t="inlineStr">
+        <is>
+          <t>2022 GSP</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
@@ -4849,10 +4912,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E45" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -4910,6 +4971,20 @@
           <t>Appendix B (vision, page 155)</t>
         </is>
       </c>
+      <c r="W45" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="X45" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y45" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="Z45" s="14" t="inlineStr">
+        <is>
+          <t>2022 GSP</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -4928,10 +5003,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E46" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -4989,6 +5062,20 @@
           <t>Appendix B (vision, page 136)</t>
         </is>
       </c>
+      <c r="W46" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="X46" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="Y46" s="14" t="n">
+        <v>109</v>
+      </c>
+      <c r="Z46" s="14" t="inlineStr">
+        <is>
+          <t>2022 GSP</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -5007,10 +5094,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E47" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -5068,6 +5153,20 @@
           <t>Appendix B (vision, page 155)</t>
         </is>
       </c>
+      <c r="W47" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="X47" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y47" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z47" s="14" t="inlineStr">
+        <is>
+          <t>2022 GSP</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -5088,10 +5187,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E48" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5164,6 +5261,10 @@
           <t>Appendix B (vision, page 120)</t>
         </is>
       </c>
+      <c r="W48" s="16" t="n"/>
+      <c r="X48" s="16" t="n"/>
+      <c r="Y48" s="16" t="n"/>
+      <c r="Z48" s="16" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -5184,10 +5285,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E49" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5260,6 +5359,10 @@
           <t>Appendix B (vision, page 121)</t>
         </is>
       </c>
+      <c r="W49" s="16" t="n"/>
+      <c r="X49" s="16" t="n"/>
+      <c r="Y49" s="16" t="n"/>
+      <c r="Z49" s="16" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -5349,6 +5452,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W50" s="16" t="n"/>
+      <c r="X50" s="16" t="n"/>
+      <c r="Y50" s="16" t="n"/>
+      <c r="Z50" s="16" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -5429,6 +5536,10 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
+      <c r="W51" s="16" t="n"/>
+      <c r="X51" s="16" t="n"/>
+      <c r="Y51" s="16" t="n"/>
+      <c r="Z51" s="16" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -5525,6 +5636,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W52" s="16" t="n"/>
+      <c r="X52" s="16" t="n"/>
+      <c r="Y52" s="16" t="n"/>
+      <c r="Z52" s="16" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -5543,10 +5658,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E53" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -5604,6 +5717,10 @@
           <t>Appendix B (vision, page 156)</t>
         </is>
       </c>
+      <c r="W53" s="16" t="n"/>
+      <c r="X53" s="16" t="n"/>
+      <c r="Y53" s="16" t="n"/>
+      <c r="Z53" s="16" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -5622,10 +5739,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E54" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -5683,6 +5798,10 @@
           <t>Appendix B (vision, page 156)</t>
         </is>
       </c>
+      <c r="W54" s="16" t="n"/>
+      <c r="X54" s="16" t="n"/>
+      <c r="Y54" s="16" t="n"/>
+      <c r="Z54" s="16" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -5701,10 +5820,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="E55" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -5762,6 +5879,10 @@
           <t>Appendix B (vision, page 137)</t>
         </is>
       </c>
+      <c r="W55" s="16" t="n"/>
+      <c r="X55" s="16" t="n"/>
+      <c r="Y55" s="16" t="n"/>
+      <c r="Z55" s="16" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -5856,6 +5977,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W56" s="16" t="n"/>
+      <c r="X56" s="16" t="n"/>
+      <c r="Y56" s="16" t="n"/>
+      <c r="Z56" s="16" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -5950,6 +6075,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W57" s="16" t="n"/>
+      <c r="X57" s="16" t="n"/>
+      <c r="Y57" s="16" t="n"/>
+      <c r="Z57" s="16" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -6044,6 +6173,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W58" s="16" t="n"/>
+      <c r="X58" s="16" t="n"/>
+      <c r="Y58" s="16" t="n"/>
+      <c r="Z58" s="16" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -6140,6 +6273,10 @@
           <t>Appendix B (vision, page 160)</t>
         </is>
       </c>
+      <c r="W59" s="16" t="n"/>
+      <c r="X59" s="16" t="n"/>
+      <c r="Y59" s="16" t="n"/>
+      <c r="Z59" s="16" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -6234,6 +6371,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W60" s="16" t="n"/>
+      <c r="X60" s="16" t="n"/>
+      <c r="Y60" s="16" t="n"/>
+      <c r="Z60" s="16" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -6330,6 +6471,10 @@
           <t>Appendix B (vision, page 164)</t>
         </is>
       </c>
+      <c r="W61" s="16" t="n"/>
+      <c r="X61" s="16" t="n"/>
+      <c r="Y61" s="16" t="n"/>
+      <c r="Z61" s="16" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -6426,6 +6571,10 @@
           <t>Appendix B (vision, page 164)</t>
         </is>
       </c>
+      <c r="W62" s="16" t="n"/>
+      <c r="X62" s="16" t="n"/>
+      <c r="Y62" s="16" t="n"/>
+      <c r="Z62" s="16" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -6520,6 +6669,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W63" s="16" t="n"/>
+      <c r="X63" s="16" t="n"/>
+      <c r="Y63" s="16" t="n"/>
+      <c r="Z63" s="16" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -6614,6 +6767,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W64" s="16" t="n"/>
+      <c r="X64" s="16" t="n"/>
+      <c r="Y64" s="16" t="n"/>
+      <c r="Z64" s="16" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -6703,6 +6860,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W65" s="16" t="n"/>
+      <c r="X65" s="16" t="n"/>
+      <c r="Y65" s="16" t="n"/>
+      <c r="Z65" s="16" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -6797,6 +6958,10 @@
           <t>Appendix B (vision, page 150)</t>
         </is>
       </c>
+      <c r="W66" s="16" t="n"/>
+      <c r="X66" s="16" t="n"/>
+      <c r="Y66" s="16" t="n"/>
+      <c r="Z66" s="16" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -6893,6 +7058,10 @@
           <t>Appendix B (vision, page 148)</t>
         </is>
       </c>
+      <c r="W67" s="16" t="n"/>
+      <c r="X67" s="16" t="n"/>
+      <c r="Y67" s="16" t="n"/>
+      <c r="Z67" s="16" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -6989,6 +7158,10 @@
           <t>Appendix B (vision, page 149)</t>
         </is>
       </c>
+      <c r="W68" s="16" t="n"/>
+      <c r="X68" s="16" t="n"/>
+      <c r="Y68" s="16" t="n"/>
+      <c r="Z68" s="16" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -7078,6 +7251,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W69" s="16" t="n"/>
+      <c r="X69" s="16" t="n"/>
+      <c r="Y69" s="16" t="n"/>
+      <c r="Z69" s="16" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -7172,6 +7349,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W70" s="16" t="n"/>
+      <c r="X70" s="16" t="n"/>
+      <c r="Y70" s="16" t="n"/>
+      <c r="Z70" s="16" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -7263,6 +7444,10 @@
           <t>Appendix B (vision, page 147)</t>
         </is>
       </c>
+      <c r="W71" s="16" t="n"/>
+      <c r="X71" s="16" t="n"/>
+      <c r="Y71" s="16" t="n"/>
+      <c r="Z71" s="16" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -7349,6 +7534,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
+      <c r="W72" s="16" t="n"/>
+      <c r="X72" s="16" t="n"/>
+      <c r="Y72" s="16" t="n"/>
+      <c r="Z72" s="16" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -7445,6 +7634,10 @@
           <t>Appendix B (vision, page 150)</t>
         </is>
       </c>
+      <c r="W73" s="16" t="n"/>
+      <c r="X73" s="16" t="n"/>
+      <c r="Y73" s="16" t="n"/>
+      <c r="Z73" s="16" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -7541,6 +7734,10 @@
           <t>Appendix B (vision, page 151)</t>
         </is>
       </c>
+      <c r="W74" s="16" t="n"/>
+      <c r="X74" s="16" t="n"/>
+      <c r="Y74" s="16" t="n"/>
+      <c r="Z74" s="16" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -7635,6 +7832,10 @@
           <t>Appendix B (vision, page 161)</t>
         </is>
       </c>
+      <c r="W75" s="16" t="n"/>
+      <c r="X75" s="16" t="n"/>
+      <c r="Y75" s="16" t="n"/>
+      <c r="Z75" s="16" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -7731,6 +7932,10 @@
           <t>Appendix B (vision, page 159)</t>
         </is>
       </c>
+      <c r="W76" s="16" t="n"/>
+      <c r="X76" s="16" t="n"/>
+      <c r="Y76" s="16" t="n"/>
+      <c r="Z76" s="16" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -7827,6 +8032,10 @@
           <t>Appendix B (vision, page 160)</t>
         </is>
       </c>
+      <c r="W77" s="16" t="n"/>
+      <c r="X77" s="16" t="n"/>
+      <c r="Y77" s="16" t="n"/>
+      <c r="Z77" s="16" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -7921,6 +8130,10 @@
           <t>Appendix B (vision, page 145)</t>
         </is>
       </c>
+      <c r="W78" s="16" t="n"/>
+      <c r="X78" s="16" t="n"/>
+      <c r="Y78" s="16" t="n"/>
+      <c r="Z78" s="16" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -8007,6 +8220,10 @@
           <t>Appendix B (vision, page 165)</t>
         </is>
       </c>
+      <c r="W79" s="16" t="n"/>
+      <c r="X79" s="16" t="n"/>
+      <c r="Y79" s="16" t="n"/>
+      <c r="Z79" s="16" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -8092,6 +8309,10 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
+      <c r="W80" s="16" t="n"/>
+      <c r="X80" s="16" t="n"/>
+      <c r="Y80" s="16" t="n"/>
+      <c r="Z80" s="16" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="C81" s="6" t="n"/>

--- a/BC Network 2026 v8.xlsx
+++ b/BC Network 2026 v8.xlsx
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="W7" s="15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X7" s="15" t="n">
         <v>115</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="W9" s="15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X9" s="15" t="n">
         <v>123</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="W12" s="15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X12" s="15" t="n">
         <v>115</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="W13" s="15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X13" s="15" t="n">
         <v>114</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="W15" s="15" t="n">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="X15" s="15" t="n">
         <v>103</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="W16" s="15" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="X16" s="15" t="n">
         <v>118</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="W19" s="15" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="X19" s="15" t="n">
         <v>74</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="W21" s="15" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="X21" s="15" t="n">
         <v>87</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="W22" s="15" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="X22" s="15" t="n">
         <v>83</v>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="W23" s="15" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="X23" s="15" t="n">
         <v>89</v>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="W24" s="15" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="X24" s="15" t="n">
         <v>59</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="W25" s="15" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="X25" s="15" t="n">
         <v>77</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="W26" s="15" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="X26" s="15" t="n">
         <v>72</v>
@@ -3253,18 +3253,18 @@
           <t>Appendix B (vision, page 161)</t>
         </is>
       </c>
-      <c r="W27" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="X27" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y27" s="15" t="n">
-        <v>102</v>
-      </c>
-      <c r="Z27" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W27" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="X27" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y27" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z27" s="14" t="inlineStr">
+        <is>
+          <t>2022 GSP</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="W28" s="15" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="X28" s="15" t="n">
         <v>94</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="W29" s="15" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="X29" s="15" t="n">
         <v>215</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E43" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4789,20 +4789,10 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W43" s="14" t="n">
-        <v>85</v>
-      </c>
-      <c r="X43" s="14" t="n">
-        <v>111</v>
-      </c>
-      <c r="Y43" s="14" t="n">
-        <v>113</v>
-      </c>
-      <c r="Z43" s="14" t="inlineStr">
-        <is>
-          <t>2022 GSP</t>
-        </is>
-      </c>
+      <c r="W43" s="16" t="n"/>
+      <c r="X43" s="16" t="n"/>
+      <c r="Y43" s="16" t="n"/>
+      <c r="Z43" s="16" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -4913,7 +4903,7 @@
         </is>
       </c>
       <c r="E45" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -4971,20 +4961,10 @@
           <t>Appendix B (vision, page 155)</t>
         </is>
       </c>
-      <c r="W45" s="14" t="n">
-        <v>85</v>
-      </c>
-      <c r="X45" s="14" t="n">
-        <v>105</v>
-      </c>
-      <c r="Y45" s="14" t="n">
-        <v>108</v>
-      </c>
-      <c r="Z45" s="14" t="inlineStr">
-        <is>
-          <t>2022 GSP</t>
-        </is>
-      </c>
+      <c r="W45" s="16" t="n"/>
+      <c r="X45" s="16" t="n"/>
+      <c r="Y45" s="16" t="n"/>
+      <c r="Z45" s="16" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -5004,7 +4984,7 @@
         </is>
       </c>
       <c r="E46" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -5062,20 +5042,10 @@
           <t>Appendix B (vision, page 136)</t>
         </is>
       </c>
-      <c r="W46" s="14" t="n">
-        <v>85</v>
-      </c>
-      <c r="X46" s="14" t="n">
-        <v>108</v>
-      </c>
-      <c r="Y46" s="14" t="n">
-        <v>109</v>
-      </c>
-      <c r="Z46" s="14" t="inlineStr">
-        <is>
-          <t>2022 GSP</t>
-        </is>
-      </c>
+      <c r="W46" s="16" t="n"/>
+      <c r="X46" s="16" t="n"/>
+      <c r="Y46" s="16" t="n"/>
+      <c r="Z46" s="16" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -5095,7 +5065,7 @@
         </is>
       </c>
       <c r="E47" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -5153,20 +5123,10 @@
           <t>Appendix B (vision, page 155)</t>
         </is>
       </c>
-      <c r="W47" s="14" t="n">
-        <v>85</v>
-      </c>
-      <c r="X47" s="14" t="n">
-        <v>95</v>
-      </c>
-      <c r="Y47" s="14" t="n">
-        <v>97</v>
-      </c>
-      <c r="Z47" s="14" t="inlineStr">
-        <is>
-          <t>2022 GSP</t>
-        </is>
-      </c>
+      <c r="W47" s="16" t="n"/>
+      <c r="X47" s="16" t="n"/>
+      <c r="Y47" s="16" t="n"/>
+      <c r="Z47" s="16" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -5188,7 +5148,7 @@
         </is>
       </c>
       <c r="E48" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5286,7 +5246,7 @@
         </is>
       </c>
       <c r="E49" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5659,7 +5619,7 @@
         </is>
       </c>
       <c r="E53" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -5740,7 +5700,7 @@
         </is>
       </c>
       <c r="E54" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -5821,7 +5781,7 @@
         </is>
       </c>
       <c r="E55" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>

--- a/BC Network 2026 v8.xlsx
+++ b/BC Network 2026 v8.xlsx
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="W15" s="15" t="n">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="X15" s="15" t="n">
         <v>103</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="W16" s="15" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="X16" s="15" t="n">
         <v>118</v>

--- a/BC Network 2026 v8.xlsx
+++ b/BC Network 2026 v8.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -57,22 +57,8 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="001E40AF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00C25A00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -91,12 +77,6 @@
         <bgColor rgb="00FFF7ED"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5E8F0"/>
-        <bgColor rgb="00D5E8F0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -110,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -141,9 +121,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -662,16 +639,16 @@
           <t>Appendix B (vision, page 123)</t>
         </is>
       </c>
-      <c r="W2" s="14" t="n">
+      <c r="W2" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="X2" s="14" t="n">
+      <c r="X2" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="Y2" s="14" t="n">
+      <c r="Y2" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="Z2" s="14" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -761,16 +738,16 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W3" s="14" t="n">
+      <c r="W3" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="X3" s="14" t="n">
+      <c r="X3" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="Y3" s="14" t="n">
+      <c r="Y3" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="Z3" s="14" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -869,16 +846,16 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W4" s="14" t="n">
+      <c r="W4" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="X4" s="14" t="n">
+      <c r="X4" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="Y4" s="14" t="n">
+      <c r="Y4" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="Z4" s="14" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -969,16 +946,16 @@
           <t>Appendix B (vision, page 124)</t>
         </is>
       </c>
-      <c r="W5" s="14" t="n">
+      <c r="W5" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="X5" s="14" t="n">
+      <c r="X5" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="Y5" s="14" t="n">
+      <c r="Y5" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="Z5" s="14" t="inlineStr">
+      <c r="Z5" s="12" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -1069,16 +1046,16 @@
           <t>Appendix B (vision, page 130)</t>
         </is>
       </c>
-      <c r="W6" s="14" t="n">
+      <c r="W6" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="X6" s="14" t="n">
+      <c r="X6" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="Y6" s="14" t="n">
+      <c r="Y6" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="Z6" s="14" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -1172,18 +1149,18 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W7" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="X7" s="15" t="n">
-        <v>115</v>
-      </c>
-      <c r="Y7" s="15" t="n">
-        <v>117</v>
-      </c>
-      <c r="Z7" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W7" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="X7" s="13" t="n">
+        <v>127</v>
+      </c>
+      <c r="Y7" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="Z7" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -1206,8 +1183,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E8" s="9" t="b">
-        <v>0</v>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -1280,10 +1259,6 @@
           <t>Appendix B (vision, page 136)</t>
         </is>
       </c>
-      <c r="W8" s="16" t="n"/>
-      <c r="X8" s="16" t="n"/>
-      <c r="Y8" s="16" t="n"/>
-      <c r="Z8" s="16" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1364,18 +1339,18 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W9" s="15" t="n">
-        <v>54</v>
-      </c>
-      <c r="X9" s="15" t="n">
-        <v>123</v>
-      </c>
-      <c r="Y9" s="15" t="n">
-        <v>125</v>
-      </c>
-      <c r="Z9" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W9" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="X9" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>136</v>
+      </c>
+      <c r="Z9" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -1472,18 +1447,18 @@
           <t>Appendix B (vision, page 133)</t>
         </is>
       </c>
-      <c r="W10" s="15" t="n">
-        <v>69</v>
-      </c>
-      <c r="X10" s="15" t="n">
-        <v>139</v>
-      </c>
-      <c r="Y10" s="15" t="n">
-        <v>141</v>
-      </c>
-      <c r="Z10" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W10" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="X10" s="13" t="n">
+        <v>138</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>140</v>
+      </c>
+      <c r="Z10" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -1575,18 +1550,18 @@
           <t>Appendix B (vision, page 132)</t>
         </is>
       </c>
-      <c r="W11" s="15" t="n">
+      <c r="W11" s="13" t="n">
         <v>66</v>
       </c>
-      <c r="X11" s="15" t="n">
-        <v>136</v>
-      </c>
-      <c r="Y11" s="15" t="n">
-        <v>138</v>
-      </c>
-      <c r="Z11" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="X11" s="13" t="n">
+        <v>132</v>
+      </c>
+      <c r="Y11" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="Z11" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -1683,18 +1658,18 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W12" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="X12" s="15" t="n">
-        <v>115</v>
-      </c>
-      <c r="Y12" s="15" t="n">
-        <v>117</v>
-      </c>
-      <c r="Z12" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W12" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="X12" s="13" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y12" s="13" t="n">
+        <v>123</v>
+      </c>
+      <c r="Z12" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -1793,18 +1768,18 @@
           <t>Appendix B (vision, page 129)</t>
         </is>
       </c>
-      <c r="W13" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="X13" s="15" t="n">
-        <v>114</v>
-      </c>
-      <c r="Y13" s="15" t="n">
-        <v>116</v>
-      </c>
-      <c r="Z13" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W13" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="X13" s="13" t="n">
+        <v>118</v>
+      </c>
+      <c r="Y13" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="Z13" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -1827,8 +1802,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E14" s="9" t="b">
-        <v>0</v>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1901,10 +1878,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W14" s="16" t="n"/>
-      <c r="X14" s="16" t="n"/>
-      <c r="Y14" s="16" t="n"/>
-      <c r="Z14" s="16" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1991,18 +1964,18 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W15" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="X15" s="15" t="n">
-        <v>103</v>
-      </c>
-      <c r="Y15" s="15" t="n">
-        <v>105</v>
-      </c>
-      <c r="Z15" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W15" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="X15" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y15" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="Z15" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -2099,18 +2072,18 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W16" s="15" t="n">
-        <v>48</v>
-      </c>
-      <c r="X16" s="15" t="n">
-        <v>118</v>
-      </c>
-      <c r="Y16" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="Z16" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W16" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="X16" s="13" t="n">
+        <v>113</v>
+      </c>
+      <c r="Y16" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="Z16" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -2209,16 +2182,16 @@
           <t>Appendix B (vision, page 163)</t>
         </is>
       </c>
-      <c r="W17" s="14" t="n">
+      <c r="W17" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="X17" s="14" t="n">
+      <c r="X17" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="Y17" s="14" t="n">
+      <c r="Y17" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="Z17" s="14" t="inlineStr">
+      <c r="Z17" s="12" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -2319,16 +2292,16 @@
           <t>Appendix B (vision, page 151)</t>
         </is>
       </c>
-      <c r="W18" s="14" t="n">
+      <c r="W18" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="X18" s="14" t="n">
+      <c r="X18" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="Y18" s="14" t="n">
+      <c r="Y18" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="Z18" s="14" t="inlineStr">
+      <c r="Z18" s="12" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -2427,18 +2400,18 @@
           <t>Appendix B (vision, page 144)</t>
         </is>
       </c>
-      <c r="W19" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="X19" s="15" t="n">
-        <v>74</v>
-      </c>
-      <c r="Y19" s="15" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z19" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W19" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="X19" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y19" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z19" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -2461,8 +2434,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E20" s="9" t="b">
-        <v>0</v>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -2528,10 +2503,6 @@
           <t>Appendix B (vision, page 157)</t>
         </is>
       </c>
-      <c r="W20" s="16" t="n"/>
-      <c r="X20" s="16" t="n"/>
-      <c r="Y20" s="16" t="n"/>
-      <c r="Z20" s="16" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -2626,18 +2597,18 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W21" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="X21" s="15" t="n">
+      <c r="W21" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="X21" s="13" t="n">
         <v>87</v>
       </c>
-      <c r="Y21" s="15" t="n">
+      <c r="Y21" s="13" t="n">
         <v>89</v>
       </c>
-      <c r="Z21" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="Z21" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -2731,18 +2702,18 @@
           <t>Appendix B (vision, page 162)</t>
         </is>
       </c>
-      <c r="W22" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="X22" s="15" t="n">
-        <v>83</v>
-      </c>
-      <c r="Y22" s="15" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z22" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W22" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="X22" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="Y22" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z22" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -2839,18 +2810,18 @@
           <t>Appendix B (vision, page 153)</t>
         </is>
       </c>
-      <c r="W23" s="15" t="n">
-        <v>31</v>
-      </c>
-      <c r="X23" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="Y23" s="15" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z23" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W23" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="X23" s="13" t="n">
+        <v>92</v>
+      </c>
+      <c r="Y23" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="Z23" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -2949,18 +2920,18 @@
           <t>Appendix B (vision, page 149)</t>
         </is>
       </c>
-      <c r="W24" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X24" s="15" t="n">
-        <v>59</v>
-      </c>
-      <c r="Y24" s="15" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z24" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W24" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="X24" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="Y24" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z24" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -3052,18 +3023,18 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W25" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="X25" s="15" t="n">
-        <v>77</v>
-      </c>
-      <c r="Y25" s="15" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z25" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W25" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="X25" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="Y25" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z25" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -3143,18 +3114,18 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W26" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X26" s="15" t="n">
-        <v>72</v>
-      </c>
-      <c r="Y26" s="15" t="n">
-        <v>74</v>
-      </c>
-      <c r="Z26" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W26" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="X26" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="Y26" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z26" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -3253,16 +3224,16 @@
           <t>Appendix B (vision, page 161)</t>
         </is>
       </c>
-      <c r="W27" s="14" t="n">
+      <c r="W27" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="X27" s="14" t="n">
+      <c r="X27" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="Y27" s="14" t="n">
+      <c r="Y27" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="Z27" s="14" t="inlineStr">
+      <c r="Z27" s="12" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -3352,18 +3323,18 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W28" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="X28" s="15" t="n">
-        <v>94</v>
-      </c>
-      <c r="Y28" s="15" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z28" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W28" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="X28" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="Y28" s="13" t="n">
+        <v>89</v>
+      </c>
+      <c r="Z28" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -3457,18 +3428,18 @@
           <t>Appendix B (vision, page 162)</t>
         </is>
       </c>
-      <c r="W29" s="15" t="n">
-        <v>159</v>
-      </c>
-      <c r="X29" s="15" t="n">
-        <v>215</v>
-      </c>
-      <c r="Y29" s="15" t="n">
-        <v>217</v>
-      </c>
-      <c r="Z29" s="15" t="inlineStr">
-        <is>
-          <t>2022 Mirror</t>
+      <c r="W29" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="X29" s="13" t="n">
+        <v>195</v>
+      </c>
+      <c r="Y29" s="13" t="n">
+        <v>197</v>
+      </c>
+      <c r="Z29" s="13" t="inlineStr">
+        <is>
+          <t>AGWL Mirror</t>
         </is>
       </c>
     </row>
@@ -3565,10 +3536,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W30" s="16" t="n"/>
-      <c r="X30" s="16" t="n"/>
-      <c r="Y30" s="16" t="n"/>
-      <c r="Z30" s="16" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -3665,10 +3632,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W31" s="16" t="n"/>
-      <c r="X31" s="16" t="n"/>
-      <c r="Y31" s="16" t="n"/>
-      <c r="Z31" s="16" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -3765,10 +3728,6 @@
           <t>Appendix B (vision, page 135)</t>
         </is>
       </c>
-      <c r="W32" s="16" t="n"/>
-      <c r="X32" s="16" t="n"/>
-      <c r="Y32" s="16" t="n"/>
-      <c r="Z32" s="16" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -3863,10 +3822,6 @@
           <t>Appendix B (vision, page 132)</t>
         </is>
       </c>
-      <c r="W33" s="16" t="n"/>
-      <c r="X33" s="16" t="n"/>
-      <c r="Y33" s="16" t="n"/>
-      <c r="Z33" s="16" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -3961,10 +3916,6 @@
           <t>Appendix B (vision, page 131)</t>
         </is>
       </c>
-      <c r="W34" s="16" t="n"/>
-      <c r="X34" s="16" t="n"/>
-      <c r="Y34" s="16" t="n"/>
-      <c r="Z34" s="16" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -4061,10 +4012,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W35" s="16" t="n"/>
-      <c r="X35" s="16" t="n"/>
-      <c r="Y35" s="16" t="n"/>
-      <c r="Z35" s="16" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -4161,10 +4108,6 @@
           <t>Appendix B (vision, page 129)</t>
         </is>
       </c>
-      <c r="W36" s="16" t="n"/>
-      <c r="X36" s="16" t="n"/>
-      <c r="Y36" s="16" t="n"/>
-      <c r="Z36" s="16" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -4261,10 +4204,6 @@
           <t>Appendix B (vision, page 130)</t>
         </is>
       </c>
-      <c r="W37" s="16" t="n"/>
-      <c r="X37" s="16" t="n"/>
-      <c r="Y37" s="16" t="n"/>
-      <c r="Z37" s="16" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -4361,10 +4300,6 @@
           <t>Appendix B (vision, page 124)</t>
         </is>
       </c>
-      <c r="W38" s="16" t="n"/>
-      <c r="X38" s="16" t="n"/>
-      <c r="Y38" s="16" t="n"/>
-      <c r="Z38" s="16" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -4461,10 +4396,6 @@
           <t>Appendix B (vision, page 125)</t>
         </is>
       </c>
-      <c r="W39" s="16" t="n"/>
-      <c r="X39" s="16" t="n"/>
-      <c r="Y39" s="16" t="n"/>
-      <c r="Z39" s="16" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -4561,10 +4492,6 @@
           <t>Appendix B (vision, page 125)</t>
         </is>
       </c>
-      <c r="W40" s="16" t="n"/>
-      <c r="X40" s="16" t="n"/>
-      <c r="Y40" s="16" t="n"/>
-      <c r="Z40" s="16" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -4626,10 +4553,6 @@
           <t>Not in BBGM. From 2025-12 Tables</t>
         </is>
       </c>
-      <c r="W41" s="16" t="n"/>
-      <c r="X41" s="16" t="n"/>
-      <c r="Y41" s="16" t="n"/>
-      <c r="Z41" s="16" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -4691,10 +4614,6 @@
           <t>Not in BBGM. From 2025-12 Tables</t>
         </is>
       </c>
-      <c r="W42" s="16" t="n"/>
-      <c r="X42" s="16" t="n"/>
-      <c r="Y42" s="16" t="n"/>
-      <c r="Z42" s="16" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -4715,8 +4634,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E43" s="8" t="b">
-        <v>0</v>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4789,10 +4710,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W43" s="16" t="n"/>
-      <c r="X43" s="16" t="n"/>
-      <c r="Y43" s="16" t="n"/>
-      <c r="Z43" s="16" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -4811,8 +4728,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E44" s="8" t="b">
-        <v>1</v>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -4870,16 +4789,16 @@
           <t>Appendix B (vision, page 157)</t>
         </is>
       </c>
-      <c r="W44" s="14" t="n">
+      <c r="W44" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="X44" s="14" t="n">
+      <c r="X44" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="Y44" s="14" t="n">
+      <c r="Y44" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="Z44" s="14" t="inlineStr">
+      <c r="Z44" s="12" t="inlineStr">
         <is>
           <t>2022 GSP</t>
         </is>
@@ -4902,8 +4821,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E45" s="8" t="b">
-        <v>0</v>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -4961,10 +4882,6 @@
           <t>Appendix B (vision, page 155)</t>
         </is>
       </c>
-      <c r="W45" s="16" t="n"/>
-      <c r="X45" s="16" t="n"/>
-      <c r="Y45" s="16" t="n"/>
-      <c r="Z45" s="16" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -4983,8 +4900,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E46" s="8" t="b">
-        <v>0</v>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
@@ -5042,10 +4961,6 @@
           <t>Appendix B (vision, page 136)</t>
         </is>
       </c>
-      <c r="W46" s="16" t="n"/>
-      <c r="X46" s="16" t="n"/>
-      <c r="Y46" s="16" t="n"/>
-      <c r="Z46" s="16" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -5064,8 +4979,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E47" s="8" t="b">
-        <v>0</v>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -5123,10 +5040,6 @@
           <t>Appendix B (vision, page 155)</t>
         </is>
       </c>
-      <c r="W47" s="16" t="n"/>
-      <c r="X47" s="16" t="n"/>
-      <c r="Y47" s="16" t="n"/>
-      <c r="Z47" s="16" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -5147,8 +5060,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E48" s="8" t="b">
-        <v>0</v>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5221,10 +5136,6 @@
           <t>Appendix B (vision, page 120)</t>
         </is>
       </c>
-      <c r="W48" s="16" t="n"/>
-      <c r="X48" s="16" t="n"/>
-      <c r="Y48" s="16" t="n"/>
-      <c r="Z48" s="16" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -5245,8 +5156,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E49" s="8" t="b">
-        <v>0</v>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5319,10 +5232,6 @@
           <t>Appendix B (vision, page 121)</t>
         </is>
       </c>
-      <c r="W49" s="16" t="n"/>
-      <c r="X49" s="16" t="n"/>
-      <c r="Y49" s="16" t="n"/>
-      <c r="Z49" s="16" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -5412,10 +5321,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W50" s="16" t="n"/>
-      <c r="X50" s="16" t="n"/>
-      <c r="Y50" s="16" t="n"/>
-      <c r="Z50" s="16" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -5496,10 +5401,6 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W51" s="16" t="n"/>
-      <c r="X51" s="16" t="n"/>
-      <c r="Y51" s="16" t="n"/>
-      <c r="Z51" s="16" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -5596,10 +5497,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W52" s="16" t="n"/>
-      <c r="X52" s="16" t="n"/>
-      <c r="Y52" s="16" t="n"/>
-      <c r="Z52" s="16" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -5618,8 +5515,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E53" s="8" t="b">
-        <v>0</v>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -5677,10 +5576,6 @@
           <t>Appendix B (vision, page 156)</t>
         </is>
       </c>
-      <c r="W53" s="16" t="n"/>
-      <c r="X53" s="16" t="n"/>
-      <c r="Y53" s="16" t="n"/>
-      <c r="Z53" s="16" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -5699,8 +5594,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E54" s="8" t="b">
-        <v>0</v>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -5758,10 +5655,6 @@
           <t>Appendix B (vision, page 156)</t>
         </is>
       </c>
-      <c r="W54" s="16" t="n"/>
-      <c r="X54" s="16" t="n"/>
-      <c r="Y54" s="16" t="n"/>
-      <c r="Z54" s="16" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -5780,8 +5673,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E55" s="8" t="b">
-        <v>0</v>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -5839,10 +5734,6 @@
           <t>Appendix B (vision, page 137)</t>
         </is>
       </c>
-      <c r="W55" s="16" t="n"/>
-      <c r="X55" s="16" t="n"/>
-      <c r="Y55" s="16" t="n"/>
-      <c r="Z55" s="16" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -5937,10 +5828,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W56" s="16" t="n"/>
-      <c r="X56" s="16" t="n"/>
-      <c r="Y56" s="16" t="n"/>
-      <c r="Z56" s="16" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -6035,10 +5922,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W57" s="16" t="n"/>
-      <c r="X57" s="16" t="n"/>
-      <c r="Y57" s="16" t="n"/>
-      <c r="Z57" s="16" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -6133,10 +6016,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W58" s="16" t="n"/>
-      <c r="X58" s="16" t="n"/>
-      <c r="Y58" s="16" t="n"/>
-      <c r="Z58" s="16" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -6233,10 +6112,6 @@
           <t>Appendix B (vision, page 160)</t>
         </is>
       </c>
-      <c r="W59" s="16" t="n"/>
-      <c r="X59" s="16" t="n"/>
-      <c r="Y59" s="16" t="n"/>
-      <c r="Z59" s="16" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -6331,10 +6206,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W60" s="16" t="n"/>
-      <c r="X60" s="16" t="n"/>
-      <c r="Y60" s="16" t="n"/>
-      <c r="Z60" s="16" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -6431,10 +6302,6 @@
           <t>Appendix B (vision, page 164)</t>
         </is>
       </c>
-      <c r="W61" s="16" t="n"/>
-      <c r="X61" s="16" t="n"/>
-      <c r="Y61" s="16" t="n"/>
-      <c r="Z61" s="16" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -6531,10 +6398,6 @@
           <t>Appendix B (vision, page 164)</t>
         </is>
       </c>
-      <c r="W62" s="16" t="n"/>
-      <c r="X62" s="16" t="n"/>
-      <c r="Y62" s="16" t="n"/>
-      <c r="Z62" s="16" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -6629,10 +6492,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W63" s="16" t="n"/>
-      <c r="X63" s="16" t="n"/>
-      <c r="Y63" s="16" t="n"/>
-      <c r="Z63" s="16" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -6727,10 +6586,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W64" s="16" t="n"/>
-      <c r="X64" s="16" t="n"/>
-      <c r="Y64" s="16" t="n"/>
-      <c r="Z64" s="16" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -6820,10 +6675,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W65" s="16" t="n"/>
-      <c r="X65" s="16" t="n"/>
-      <c r="Y65" s="16" t="n"/>
-      <c r="Z65" s="16" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -6918,10 +6769,6 @@
           <t>Appendix B (vision, page 150)</t>
         </is>
       </c>
-      <c r="W66" s="16" t="n"/>
-      <c r="X66" s="16" t="n"/>
-      <c r="Y66" s="16" t="n"/>
-      <c r="Z66" s="16" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -7018,10 +6865,6 @@
           <t>Appendix B (vision, page 148)</t>
         </is>
       </c>
-      <c r="W67" s="16" t="n"/>
-      <c r="X67" s="16" t="n"/>
-      <c r="Y67" s="16" t="n"/>
-      <c r="Z67" s="16" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -7118,10 +6961,6 @@
           <t>Appendix B (vision, page 149)</t>
         </is>
       </c>
-      <c r="W68" s="16" t="n"/>
-      <c r="X68" s="16" t="n"/>
-      <c r="Y68" s="16" t="n"/>
-      <c r="Z68" s="16" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -7211,10 +7050,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W69" s="16" t="n"/>
-      <c r="X69" s="16" t="n"/>
-      <c r="Y69" s="16" t="n"/>
-      <c r="Z69" s="16" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -7309,10 +7144,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W70" s="16" t="n"/>
-      <c r="X70" s="16" t="n"/>
-      <c r="Y70" s="16" t="n"/>
-      <c r="Z70" s="16" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -7404,10 +7235,6 @@
           <t>Appendix B (vision, page 147)</t>
         </is>
       </c>
-      <c r="W71" s="16" t="n"/>
-      <c r="X71" s="16" t="n"/>
-      <c r="Y71" s="16" t="n"/>
-      <c r="Z71" s="16" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -7494,10 +7321,6 @@
           <t>Appendix B (OCR)</t>
         </is>
       </c>
-      <c r="W72" s="16" t="n"/>
-      <c r="X72" s="16" t="n"/>
-      <c r="Y72" s="16" t="n"/>
-      <c r="Z72" s="16" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -7594,10 +7417,6 @@
           <t>Appendix B (vision, page 150)</t>
         </is>
       </c>
-      <c r="W73" s="16" t="n"/>
-      <c r="X73" s="16" t="n"/>
-      <c r="Y73" s="16" t="n"/>
-      <c r="Z73" s="16" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -7694,10 +7513,6 @@
           <t>Appendix B (vision, page 151)</t>
         </is>
       </c>
-      <c r="W74" s="16" t="n"/>
-      <c r="X74" s="16" t="n"/>
-      <c r="Y74" s="16" t="n"/>
-      <c r="Z74" s="16" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -7792,10 +7607,6 @@
           <t>Appendix B (vision, page 161)</t>
         </is>
       </c>
-      <c r="W75" s="16" t="n"/>
-      <c r="X75" s="16" t="n"/>
-      <c r="Y75" s="16" t="n"/>
-      <c r="Z75" s="16" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -7892,10 +7703,6 @@
           <t>Appendix B (vision, page 159)</t>
         </is>
       </c>
-      <c r="W76" s="16" t="n"/>
-      <c r="X76" s="16" t="n"/>
-      <c r="Y76" s="16" t="n"/>
-      <c r="Z76" s="16" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -7992,10 +7799,6 @@
           <t>Appendix B (vision, page 160)</t>
         </is>
       </c>
-      <c r="W77" s="16" t="n"/>
-      <c r="X77" s="16" t="n"/>
-      <c r="Y77" s="16" t="n"/>
-      <c r="Z77" s="16" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -8090,10 +7893,6 @@
           <t>Appendix B (vision, page 145)</t>
         </is>
       </c>
-      <c r="W78" s="16" t="n"/>
-      <c r="X78" s="16" t="n"/>
-      <c r="Y78" s="16" t="n"/>
-      <c r="Z78" s="16" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -8180,10 +7979,6 @@
           <t>Appendix B (vision, page 165)</t>
         </is>
       </c>
-      <c r="W79" s="16" t="n"/>
-      <c r="X79" s="16" t="n"/>
-      <c r="Y79" s="16" t="n"/>
-      <c r="Z79" s="16" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -8269,10 +8064,6 @@
           <t>Not in BBGM-2020 calibration set</t>
         </is>
       </c>
-      <c r="W80" s="16" t="n"/>
-      <c r="X80" s="16" t="n"/>
-      <c r="Y80" s="16" t="n"/>
-      <c r="Z80" s="16" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="C81" s="6" t="n"/>

--- a/BC Network 2026 v8.xlsx
+++ b/BC Network 2026 v8.xlsx
@@ -4882,6 +4882,20 @@
           <t>Appendix B (vision, page 155)</t>
         </is>
       </c>
+      <c r="W45" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="X45" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y45" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="Z45" s="12" t="inlineStr">
+        <is>
+          <t>2022 GSP</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -4961,6 +4975,20 @@
           <t>Appendix B (vision, page 136)</t>
         </is>
       </c>
+      <c r="W46" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="X46" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="Y46" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="Z46" s="12" t="inlineStr">
+        <is>
+          <t>2022 GSP</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -5038,6 +5066,20 @@
       <c r="V47" s="5" t="inlineStr">
         <is>
           <t>Appendix B (vision, page 155)</t>
+        </is>
+      </c>
+      <c r="W47" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="X47" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y47" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z47" s="12" t="inlineStr">
+        <is>
+          <t>2022 GSP</t>
         </is>
       </c>
     </row>
